--- a/public/templates/bdd_costo_mensual.xlsx
+++ b/public/templates/bdd_costo_mensual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\tierrasanta\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD8FC0F-0FFC-4D7D-9F17-AFAE8237D28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F07613-1113-4B82-89AF-3258EE8D4004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Área</t>
   </si>
@@ -154,6 +154,12 @@
   </si>
   <si>
     <t>COSTO TOTAL</t>
+  </si>
+  <si>
+    <t>PLANILLA BONO PRODUCTIVIDAD</t>
+  </si>
+  <si>
+    <t>BONO PRODUCTIVIDAD</t>
   </si>
 </sst>
 </file>
@@ -439,7 +445,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -552,6 +558,28 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -575,24 +603,6 @@
     <xf numFmtId="2" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -626,24 +636,21 @@
     <xf numFmtId="4" fontId="10" fillId="8" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;S/&quot;\ * #,##0.00_-;\-&quot;S/&quot;\ * #,##0.00_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="26">
     <dxf>
       <font>
         <b val="0"/>
@@ -661,85 +668,13 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;S/&quot;\ * #,##0.00_-;\-&quot;S/&quot;\ * #,##0.00_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -764,21 +699,139 @@
           <bgColor rgb="FF1F4E86"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;S/&quot;\ * #,##0.00_-;\-&quot;S/&quot;\ * #,##0.00_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;S/&quot;\ * #,##0.00_-;\-&quot;S/&quot;\ * #,##0.00_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -864,34 +917,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{275C6DC4-33E2-4EB2-B71A-B63A2C67D21D}" name="tblCostoPlanillaMensual" displayName="tblCostoPlanillaMensual" ref="A7:F8" insertRow="1" totalsRowShown="0" headerRowDxfId="22">
-  <autoFilter ref="A7:F8" xr:uid="{275C6DC4-33E2-4EB2-B71A-B63A2C67D21D}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{C159FE92-5B01-449F-AE71-631BD254E04E}" name="N°" dataDxfId="17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{275C6DC4-33E2-4EB2-B71A-B63A2C67D21D}" name="tblCostoPlanillaMensual" displayName="tblCostoPlanillaMensual" ref="A7:G8" insertRow="1" totalsRowShown="0" headerRowDxfId="25">
+  <autoFilter ref="A7:G8" xr:uid="{275C6DC4-33E2-4EB2-B71A-B63A2C67D21D}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{C159FE92-5B01-449F-AE71-631BD254E04E}" name="N°" dataDxfId="24"/>
     <tableColumn id="2" xr3:uid="{9B89B643-F63A-4A0F-AE6A-F929AFBC4D17}" name="NOMBRE EMPLEADO"/>
-    <tableColumn id="3" xr3:uid="{8DF0E71C-85BD-40A6-ABCB-35E28C3BD8FC}" name="SUELDO PAGADO" dataDxfId="21" dataCellStyle="Moneda"/>
-    <tableColumn id="4" xr3:uid="{B8FBA746-56FE-4F19-8E41-2ED4542BF715}" name="APORTES DEL TRABAJADOR" dataDxfId="20" dataCellStyle="Moneda"/>
-    <tableColumn id="5" xr3:uid="{5412C88C-65A9-4EE3-881F-5A88455AEA6F}" name="APORTES DEL EMPLEADOR" dataDxfId="19" dataCellStyle="Moneda"/>
-    <tableColumn id="6" xr3:uid="{453B62C9-7CEA-4FE5-AA62-8A3BEE898C21}" name="COSTO TOTAL EMPRESA" dataDxfId="18" dataCellStyle="Moneda"/>
+    <tableColumn id="3" xr3:uid="{8DF0E71C-85BD-40A6-ABCB-35E28C3BD8FC}" name="SUELDO PAGADO" dataDxfId="23" dataCellStyle="Moneda"/>
+    <tableColumn id="4" xr3:uid="{B8FBA746-56FE-4F19-8E41-2ED4542BF715}" name="APORTES DEL TRABAJADOR" dataDxfId="22" dataCellStyle="Moneda"/>
+    <tableColumn id="5" xr3:uid="{5412C88C-65A9-4EE3-881F-5A88455AEA6F}" name="APORTES DEL EMPLEADOR" dataDxfId="1" dataCellStyle="Moneda"/>
+    <tableColumn id="7" xr3:uid="{B7B7AFD8-71E1-457D-8557-B2A6A4E3A9D2}" name="BONO PRODUCTIVIDAD" dataDxfId="0" dataCellStyle="Moneda"/>
+    <tableColumn id="6" xr3:uid="{453B62C9-7CEA-4FE5-AA62-8A3BEE898C21}" name="COSTO TOTAL EMPRESA" dataDxfId="2" dataCellStyle="Moneda"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F06A4B39-294C-420F-97C4-E54FE34E21EC}" name="Tabla2" displayName="Tabla2" ref="A4:H7" headerRowDxfId="16">
-  <autoFilter ref="A4:H7" xr:uid="{F06A4B39-294C-420F-97C4-E54FE34E21EC}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{2907273D-C11E-4E1E-9EB3-02BD1CC84CA6}" name="MES" totalsRowLabel="Total" dataDxfId="15" totalsRowDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{9CD235A8-2235-4B0D-8DB1-99F5B4282247}" name="PLANILLA" dataDxfId="0" totalsRowDxfId="2" dataCellStyle="Moneda">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F06A4B39-294C-420F-97C4-E54FE34E21EC}" name="Tabla2" displayName="Tabla2" ref="A4:I7" headerRowDxfId="3">
+  <autoFilter ref="A4:I7" xr:uid="{F06A4B39-294C-420F-97C4-E54FE34E21EC}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{2907273D-C11E-4E1E-9EB3-02BD1CC84CA6}" name="MES" totalsRowLabel="Total" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{9CD235A8-2235-4B0D-8DB1-99F5B4282247}" name="PLANILLA" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Moneda">
       <calculatedColumnFormula>B3-B4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{58D81BF4-3D56-4616-9378-B15ACCE87B7C}" name="CUADRILLA" dataDxfId="14" totalsRowDxfId="3" dataCellStyle="Moneda"/>
-    <tableColumn id="4" xr3:uid="{A02A0E9E-FDFD-42C6-AD5C-FBB28DC980FA}" name="MAQUINARIA" dataDxfId="13" totalsRowDxfId="4" dataCellStyle="Moneda"/>
-    <tableColumn id="5" xr3:uid="{C67ABD93-7F07-4989-AA06-CC63EDDBCE7D}" name="PESTICIDAS" dataDxfId="12" totalsRowDxfId="5" dataCellStyle="Moneda"/>
-    <tableColumn id="6" xr3:uid="{5509C64D-975E-4FA2-A434-70C957CCAFD9}" name="FERTILIZANTES" dataDxfId="11" totalsRowDxfId="6" dataCellStyle="Moneda"/>
-    <tableColumn id="7" xr3:uid="{ADA849BF-730B-440E-B74D-D2BED82DE221}" name="GENERALES" totalsRowFunction="count" dataDxfId="10" totalsRowDxfId="7" dataCellStyle="Moneda"/>
-    <tableColumn id="8" xr3:uid="{6750E0BA-AD48-4AA8-8A44-1D8F376B103D}" name="COSTO TOTAL" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Moneda" totalsRowCellStyle="Moneda">
+    <tableColumn id="9" xr3:uid="{4F0CC146-7C00-4621-932D-4F8FF6524B32}" name="PLANILLA BONO PRODUCTIVIDAD" dataDxfId="4" totalsRowDxfId="5" dataCellStyle="Moneda"/>
+    <tableColumn id="3" xr3:uid="{58D81BF4-3D56-4616-9378-B15ACCE87B7C}" name="CUADRILLA" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Moneda"/>
+    <tableColumn id="4" xr3:uid="{A02A0E9E-FDFD-42C6-AD5C-FBB28DC980FA}" name="MAQUINARIA" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Moneda"/>
+    <tableColumn id="5" xr3:uid="{C67ABD93-7F07-4989-AA06-CC63EDDBCE7D}" name="PESTICIDAS" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Moneda"/>
+    <tableColumn id="6" xr3:uid="{5509C64D-975E-4FA2-A434-70C957CCAFD9}" name="FERTILIZANTES" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Moneda"/>
+    <tableColumn id="7" xr3:uid="{ADA849BF-730B-440E-B74D-D2BED82DE221}" name="GENERALES" totalsRowFunction="count" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Moneda"/>
+    <tableColumn id="8" xr3:uid="{6750E0BA-AD48-4AA8-8A44-1D8F376B103D}" name="COSTO TOTAL" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Moneda" totalsRowCellStyle="Moneda">
       <calculatedColumnFormula>SUM(Tabla2[[#This Row],[PLANILLA]:[GENERALES]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1243,20 +1298,20 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
     </row>
     <row r="2" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
@@ -1276,43 +1331,43 @@
       <c r="M2" s="6"/>
     </row>
     <row r="3" spans="1:13" s="11" customFormat="1" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="39"/>
-      <c r="G3" s="38" t="s">
+      <c r="F3" s="47"/>
+      <c r="G3" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="38"/>
-      <c r="I3" s="40" t="s">
+      <c r="H3" s="46"/>
+      <c r="I3" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="45" t="s">
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="34" t="s">
+      <c r="M3" s="42" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="11" customFormat="1" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
       <c r="E4" s="8" t="s">
         <v>14</v>
       </c>
@@ -1334,22 +1389,22 @@
       <c r="K4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="46"/>
-      <c r="M4" s="35"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="43"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:M4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="10">
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I3:K3"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="I3:K3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1357,73 +1412,78 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4CC069E-D230-4B98-BB8C-3C83E4AA3032}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" style="30" customWidth="1"/>
     <col min="2" max="2" width="41.5546875" customWidth="1"/>
     <col min="3" max="4" width="16.88671875" style="25" customWidth="1"/>
-    <col min="5" max="6" width="24.5546875" style="25" customWidth="1"/>
+    <col min="5" max="7" width="24.5546875" style="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
     </row>
-    <row r="2" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="s">
+    <row r="2" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
     </row>
-    <row r="3" spans="1:6" ht="4.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="50" t="s">
+    <row r="3" spans="1:7" ht="4.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="54" t="s">
+      <c r="B4" s="53"/>
+      <c r="C4" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="55"/>
+      <c r="D4" s="57"/>
       <c r="E4" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="31"/>
+      <c r="G4" s="31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="52"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="56">
+    <row r="5" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="54"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="58">
         <f>SUM(tblCostoPlanillaMensual[COSTO TOTAL EMPRESA])</f>
         <v>0</v>
       </c>
-      <c r="D5" s="57"/>
+      <c r="D5" s="59"/>
       <c r="E5" s="33">
         <f>COUNTA(tblCostoPlanillaMensual[N°])</f>
         <v>0</v>
       </c>
-      <c r="F5" s="32"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="32"/>
     </row>
-    <row r="6" spans="1:6" ht="4.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="4.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
     </row>
-    <row r="7" spans="1:6" s="27" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" s="27" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
         <v>22</v>
       </c>
@@ -1440,13 +1500,19 @@
         <v>20</v>
       </c>
       <c r="F7" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="29" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F8" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C4:D4"/>
@@ -1463,130 +1529,141 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF17FEE-781B-4A30-8714-7E571BDE43A7}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.6640625" customWidth="1"/>
-    <col min="2" max="8" width="20.5546875" customWidth="1"/>
+    <col min="2" max="9" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
     </row>
-    <row r="2" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="s">
+    <row r="2" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="59" t="s">
+    <row r="4" spans="1:9" s="61" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="60" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="60" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="E4" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="F4" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="60" t="s">
+      <c r="G4" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="60" t="s">
+      <c r="H4" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="59" t="s">
+      <c r="I4" s="60" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="58" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61">
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35">
         <f>SUM(Tabla2[[#This Row],[PLANILLA]:[GENERALES]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="58" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61">
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35">
         <f>SUM(Tabla2[[#This Row],[PLANILLA]:[GENERALES]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="58" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="61">
-        <f t="shared" ref="B5:B7" si="0">B5-B6</f>
+      <c r="B7" s="35">
+        <f t="shared" ref="B7:C7" si="0">B5-B6</f>
         <v>0</v>
       </c>
-      <c r="C7" s="61">
-        <f t="shared" ref="C7" si="1">C5-C6</f>
+      <c r="C7" s="35">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D7" s="61">
-        <f t="shared" ref="D7" si="2">D5-D6</f>
+      <c r="D7" s="35">
+        <f t="shared" ref="D7" si="1">D5-D6</f>
         <v>0</v>
       </c>
-      <c r="E7" s="61">
-        <f t="shared" ref="E7" si="3">E5-E6</f>
+      <c r="E7" s="35">
+        <f t="shared" ref="E7" si="2">E5-E6</f>
         <v>0</v>
       </c>
-      <c r="F7" s="61">
-        <f t="shared" ref="F7" si="4">F5-F6</f>
+      <c r="F7" s="35">
+        <f t="shared" ref="F7" si="3">F5-F6</f>
         <v>0</v>
       </c>
-      <c r="G7" s="61">
-        <f t="shared" ref="G7" si="5">G5-G6</f>
+      <c r="G7" s="35">
+        <f t="shared" ref="G7" si="4">G5-G6</f>
         <v>0</v>
       </c>
-      <c r="H7" s="61">
-        <f t="shared" ref="H7" si="6">H5-H6</f>
+      <c r="H7" s="35">
+        <f t="shared" ref="H7" si="5">H5-H6</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="35">
+        <f t="shared" ref="I7" si="6">I5-I6</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
